--- a/data/inst_7_dia_1.xlsx
+++ b/data/inst_7_dia_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flexible-vrp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TFG\Flexible\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ADD68A-AE69-4896-8D5E-0C738BB29F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528F2C5F-3BC8-494B-983F-CD78CCC3B3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -252,9 +252,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -292,7 +292,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -398,7 +398,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -540,7 +540,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -549,12 +549,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -570,7 +570,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -578,7 +578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -586,7 +586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -594,7 +594,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -602,7 +602,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -610,7 +610,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -618,7 +618,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -626,7 +626,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -634,7 +634,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -643,15 +643,15 @@
         <v>17.857142857142858</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
       <c r="B12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -659,7 +659,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -676,12 +676,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -692,7 +692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -714,7 +714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -725,7 +725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -736,7 +736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -747,7 +747,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -758,7 +758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -769,7 +769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -780,7 +780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -791,7 +791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -813,7 +813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -824,7 +824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -835,7 +835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -846,7 +846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -857,7 +857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -868,7 +868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -879,7 +879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -890,7 +890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -901,7 +901,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -912,7 +912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -923,7 +923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -934,7 +934,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -945,7 +945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -956,7 +956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -967,7 +967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -978,7 +978,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -989,7 +989,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>16</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -1317,9 +1317,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
